--- a/Result/profitability/2481.xlsx
+++ b/Result/profitability/2481.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.645</v>
+        <v>0.7224999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>29.15875</v>
+        <v>29.66</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.60375</v>
+        <v>0.6962499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>28.15</v>
+        <v>28.41</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.60625</v>
+        <v>0.67625</v>
       </c>
       <c r="N4" t="n">
-        <v>25.90875</v>
+        <v>26.27</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46875</v>
+        <v>0.54625</v>
       </c>
       <c r="N5" t="n">
-        <v>24.2425</v>
+        <v>24.5625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32125</v>
+        <v>0.3825</v>
       </c>
       <c r="N6" t="n">
-        <v>22.01</v>
+        <v>22.24875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21875</v>
+        <v>0.26125</v>
       </c>
       <c r="N7" t="n">
-        <v>19.605</v>
+        <v>19.67375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.135</v>
+        <v>0.20125</v>
       </c>
       <c r="N8" t="n">
-        <v>18.07375</v>
+        <v>18.13375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3956</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2641</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1314</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>464</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>183</v>
+      </c>
+      <c r="J75" t="n">
+        <v>647</v>
+      </c>
+      <c r="K75" t="n">
+        <v>488</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7066666666666668</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4799999999999969</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01466096518020765</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08349641226353555</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
